--- a/runs/RELX/2026-10-14/bear/scratch/s_stack_324/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/s_stack_324/out/dcf.xlsx
@@ -539,11 +539,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.08731596390032623</v>
+        <v>0.08965947737385002</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PM rule: return on new investment 10.6% (value driver formula, briefs/RELX.yaml)</t>
+          <t>PM rule: return on new investment 9.9% (value driver formula, briefs/RELX.yaml)</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1612.308079854636</v>
+        <v>1657.996253475753</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.103145</v>
+        <v>0.0953618</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09615342190000001</v>
+        <v>0.089367872476</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>8774.992631812014</v>
+        <v>8908.190278071177</v>
       </c>
     </row>
     <row r="21">
@@ -1448,7 +1448,7 @@
         <v/>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2541.692043806841</v>
+        <v>2513.132811760127</v>
       </c>
     </row>
     <row r="22">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>31319.59175965247</v>
+        <v>33793.25948273113</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>20720.25256150393</v>
+        <v>22990.2953075293</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>29495.24519331595</v>
+        <v>31898.48558560048</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>22498.24519331595</v>
+        <v>24901.48558560048</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>21023.86672233645</v>
+        <v>23470.4699162845</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>12.05666507841183</v>
+        <v>13.45973120695919</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1205.666507841183</v>
+        <v>1345.973120695919</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.5648984093</v>
+        <v>-0.5142644819</v>
       </c>
     </row>
   </sheetData>
